--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +817,1240 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121560743</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90719</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567117</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6681766</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121560757</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5172</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567080</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6681863</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121560741</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90719</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567125</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6681657</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121560744</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>567019</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6681902</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121560755</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90932</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>567118</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6681765</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121560750</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91112</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>567116</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6681765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121560742</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90719</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>567120</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6681651</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121560745</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91159</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>567091</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6681781</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121560746</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91159</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>567115</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6681763</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121560761</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105765</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>567046</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6681865</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121560747</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>567124</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6681658</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121560740</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90684</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>567030</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6681856</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560757</v>
+        <v>121560741</v>
       </c>
       <c r="B4" t="n">
-        <v>5172</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,43 +934,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567080</v>
+        <v>567125</v>
       </c>
       <c r="R4" t="n">
-        <v>6681863</v>
+        <v>6681657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560741</v>
+        <v>121560761</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>105765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1036,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220785</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567125</v>
+        <v>567046</v>
       </c>
       <c r="R5" t="n">
-        <v>6681657</v>
+        <v>6681865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,6 +1100,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560744</v>
+        <v>121560746</v>
       </c>
       <c r="B6" t="n">
-        <v>57371</v>
+        <v>91159</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,43 +1143,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567019</v>
+        <v>567115</v>
       </c>
       <c r="R6" t="n">
-        <v>6681902</v>
+        <v>6681763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1340,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560750</v>
+        <v>121560745</v>
       </c>
       <c r="B8" t="n">
-        <v>91112</v>
+        <v>91159</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,20 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567116</v>
+        <v>567091</v>
       </c>
       <c r="R8" t="n">
-        <v>6681765</v>
+        <v>6681781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560742</v>
+        <v>121560740</v>
       </c>
       <c r="B9" t="n">
-        <v>90719</v>
+        <v>90684</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1449,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567120</v>
+        <v>567030</v>
       </c>
       <c r="R9" t="n">
-        <v>6681651</v>
+        <v>6681856</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560745</v>
+        <v>121560757</v>
       </c>
       <c r="B10" t="n">
-        <v>91159</v>
+        <v>5172</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,38 +1551,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567091</v>
+        <v>567080</v>
       </c>
       <c r="R10" t="n">
-        <v>6681781</v>
+        <v>6681863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560746</v>
+        <v>121560750</v>
       </c>
       <c r="B11" t="n">
-        <v>91159</v>
+        <v>91112</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1653,25 +1658,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567115</v>
+        <v>567116</v>
       </c>
       <c r="R11" t="n">
-        <v>6681763</v>
+        <v>6681765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560761</v>
+        <v>121560742</v>
       </c>
       <c r="B12" t="n">
-        <v>105765</v>
+        <v>90719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567046</v>
+        <v>567120</v>
       </c>
       <c r="R12" t="n">
-        <v>6681865</v>
+        <v>6681651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,11 +1819,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560747</v>
+        <v>121560744</v>
       </c>
       <c r="B13" t="n">
-        <v>91005</v>
+        <v>57371</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,34 +1861,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567124</v>
+        <v>567019</v>
       </c>
       <c r="R13" t="n">
-        <v>6681658</v>
+        <v>6681902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560740</v>
+        <v>121560747</v>
       </c>
       <c r="B14" t="n">
-        <v>90684</v>
+        <v>91005</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567030</v>
+        <v>567124</v>
       </c>
       <c r="R14" t="n">
-        <v>6681856</v>
+        <v>6681658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560743</v>
+        <v>121560757</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,38 +832,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567117</v>
+        <v>567080</v>
       </c>
       <c r="R3" t="n">
-        <v>6681766</v>
+        <v>6681863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560741</v>
+        <v>121560745</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>91160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567125</v>
+        <v>567091</v>
       </c>
       <c r="R4" t="n">
-        <v>6681657</v>
+        <v>6681781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560761</v>
+        <v>121560746</v>
       </c>
       <c r="B5" t="n">
-        <v>105765</v>
+        <v>91160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567046</v>
+        <v>567115</v>
       </c>
       <c r="R5" t="n">
-        <v>6681865</v>
+        <v>6681763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,11 +1105,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560746</v>
+        <v>121560755</v>
       </c>
       <c r="B6" t="n">
-        <v>91159</v>
+        <v>90933</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1618</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567115</v>
+        <v>567118</v>
       </c>
       <c r="R6" t="n">
-        <v>6681763</v>
+        <v>6681765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560755</v>
+        <v>121560747</v>
       </c>
       <c r="B7" t="n">
-        <v>90932</v>
+        <v>91006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1618</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567118</v>
+        <v>567124</v>
       </c>
       <c r="R7" t="n">
-        <v>6681765</v>
+        <v>6681658</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560745</v>
+        <v>121560742</v>
       </c>
       <c r="B8" t="n">
-        <v>91159</v>
+        <v>90720</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567091</v>
+        <v>567120</v>
       </c>
       <c r="R8" t="n">
-        <v>6681781</v>
+        <v>6681651</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1440,7 @@
         <v>121560740</v>
       </c>
       <c r="B9" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560757</v>
+        <v>121560761</v>
       </c>
       <c r="B10" t="n">
-        <v>5172</v>
+        <v>105766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,43 +1551,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567080</v>
+        <v>567046</v>
       </c>
       <c r="R10" t="n">
-        <v>6681863</v>
+        <v>6681865</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,6 +1615,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,7 +1649,7 @@
         <v>121560750</v>
       </c>
       <c r="B11" t="n">
-        <v>91112</v>
+        <v>91113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560742</v>
+        <v>121560743</v>
       </c>
       <c r="B12" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567120</v>
+        <v>567117</v>
       </c>
       <c r="R12" t="n">
-        <v>6681651</v>
+        <v>6681766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1848,7 @@
         <v>121560744</v>
       </c>
       <c r="B13" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560747</v>
+        <v>121560741</v>
       </c>
       <c r="B14" t="n">
-        <v>91005</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567124</v>
+        <v>567125</v>
       </c>
       <c r="R14" t="n">
-        <v>6681658</v>
+        <v>6681657</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560757</v>
+        <v>121560740</v>
       </c>
       <c r="B3" t="n">
-        <v>5172</v>
+        <v>90685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,39 +836,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567080</v>
+        <v>567030</v>
       </c>
       <c r="R3" t="n">
-        <v>6681863</v>
+        <v>6681856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -927,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560745</v>
+        <v>121560743</v>
       </c>
       <c r="B4" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567091</v>
+        <v>567117</v>
       </c>
       <c r="R4" t="n">
-        <v>6681781</v>
+        <v>6681766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560746</v>
+        <v>121560757</v>
       </c>
       <c r="B5" t="n">
-        <v>91160</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1036,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567115</v>
+        <v>567080</v>
       </c>
       <c r="R5" t="n">
-        <v>6681763</v>
+        <v>6681863</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560755</v>
+        <v>121560745</v>
       </c>
       <c r="B6" t="n">
-        <v>90933</v>
+        <v>91160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1618</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567118</v>
+        <v>567091</v>
       </c>
       <c r="R6" t="n">
-        <v>6681765</v>
+        <v>6681781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560747</v>
+        <v>121560750</v>
       </c>
       <c r="B7" t="n">
-        <v>91006</v>
+        <v>91113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,21 +1249,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567124</v>
+        <v>567116</v>
       </c>
       <c r="R7" t="n">
-        <v>6681658</v>
+        <v>6681765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1330,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560742</v>
+        <v>121560741</v>
       </c>
       <c r="B8" t="n">
         <v>90720</v>
@@ -1375,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567120</v>
+        <v>567125</v>
       </c>
       <c r="R8" t="n">
-        <v>6681651</v>
+        <v>6681657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560740</v>
+        <v>121560747</v>
       </c>
       <c r="B9" t="n">
-        <v>90685</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567030</v>
+        <v>567124</v>
       </c>
       <c r="R9" t="n">
-        <v>6681856</v>
+        <v>6681658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1646,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560750</v>
+        <v>121560744</v>
       </c>
       <c r="B11" t="n">
-        <v>91113</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,29 +1657,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567116</v>
+        <v>567019</v>
       </c>
       <c r="R11" t="n">
-        <v>6681765</v>
+        <v>6681902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560743</v>
+        <v>121560755</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>90933</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567117</v>
+        <v>567118</v>
       </c>
       <c r="R12" t="n">
-        <v>6681766</v>
+        <v>6681765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560744</v>
+        <v>121560746</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>91160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,43 +1862,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567019</v>
+        <v>567115</v>
       </c>
       <c r="R13" t="n">
-        <v>6681902</v>
+        <v>6681763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560741</v>
+        <v>121560742</v>
       </c>
       <c r="B14" t="n">
         <v>90720</v>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567125</v>
+        <v>567120</v>
       </c>
       <c r="R14" t="n">
-        <v>6681657</v>
+        <v>6681651</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560740</v>
+        <v>121560742</v>
       </c>
       <c r="B3" t="n">
-        <v>90685</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567030</v>
+        <v>567120</v>
       </c>
       <c r="R3" t="n">
-        <v>6681856</v>
+        <v>6681651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560743</v>
+        <v>121560744</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,34 +938,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567117</v>
+        <v>567019</v>
       </c>
       <c r="R4" t="n">
-        <v>6681766</v>
+        <v>6681902</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560757</v>
+        <v>121560740</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>90685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,39 +1045,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567080</v>
+        <v>567030</v>
       </c>
       <c r="R5" t="n">
-        <v>6681863</v>
+        <v>6681856</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560745</v>
+        <v>121560741</v>
       </c>
       <c r="B6" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567091</v>
+        <v>567125</v>
       </c>
       <c r="R6" t="n">
-        <v>6681781</v>
+        <v>6681657</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560750</v>
+        <v>121560755</v>
       </c>
       <c r="B7" t="n">
-        <v>91113</v>
+        <v>90933</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,20 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>1618</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,7 +1273,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567116</v>
+        <v>567118</v>
       </c>
       <c r="R7" t="n">
         <v>6681765</v>
@@ -1330,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560741</v>
+        <v>121560757</v>
       </c>
       <c r="B8" t="n">
-        <v>90720</v>
+        <v>5172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,38 +1347,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567125</v>
+        <v>567080</v>
       </c>
       <c r="R8" t="n">
-        <v>6681657</v>
+        <v>6681863</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560747</v>
+        <v>121560761</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>105766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567124</v>
+        <v>567046</v>
       </c>
       <c r="R9" t="n">
-        <v>6681658</v>
+        <v>6681865</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1508,6 +1518,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560761</v>
+        <v>121560746</v>
       </c>
       <c r="B10" t="n">
-        <v>105766</v>
+        <v>91160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,25 +1561,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567046</v>
+        <v>567115</v>
       </c>
       <c r="R10" t="n">
-        <v>6681865</v>
+        <v>6681763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,11 +1625,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560744</v>
+        <v>121560750</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>91113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,39 +1667,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567019</v>
+        <v>567116</v>
       </c>
       <c r="R11" t="n">
-        <v>6681902</v>
+        <v>6681765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560755</v>
+        <v>121560745</v>
       </c>
       <c r="B12" t="n">
-        <v>90933</v>
+        <v>91160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1618</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567118</v>
+        <v>567091</v>
       </c>
       <c r="R12" t="n">
-        <v>6681765</v>
+        <v>6681781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560746</v>
+        <v>121560743</v>
       </c>
       <c r="B13" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567115</v>
+        <v>567117</v>
       </c>
       <c r="R13" t="n">
-        <v>6681763</v>
+        <v>6681766</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560742</v>
+        <v>121560747</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567120</v>
+        <v>567124</v>
       </c>
       <c r="R14" t="n">
-        <v>6681651</v>
+        <v>6681658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560742</v>
+        <v>121560744</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,34 +836,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567120</v>
+        <v>567019</v>
       </c>
       <c r="R3" t="n">
-        <v>6681651</v>
+        <v>6681902</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560744</v>
+        <v>121560741</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,39 +943,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567019</v>
+        <v>567125</v>
       </c>
       <c r="R4" t="n">
-        <v>6681902</v>
+        <v>6681657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560740</v>
+        <v>121560750</v>
       </c>
       <c r="B5" t="n">
-        <v>90685</v>
+        <v>91113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1041,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567030</v>
+        <v>567116</v>
       </c>
       <c r="R5" t="n">
-        <v>6681856</v>
+        <v>6681765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560741</v>
+        <v>121560747</v>
       </c>
       <c r="B6" t="n">
-        <v>90720</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567125</v>
+        <v>567124</v>
       </c>
       <c r="R6" t="n">
-        <v>6681657</v>
+        <v>6681658</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560755</v>
+        <v>121560746</v>
       </c>
       <c r="B7" t="n">
-        <v>90933</v>
+        <v>91160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,21 +1244,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1618</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567118</v>
+        <v>567115</v>
       </c>
       <c r="R7" t="n">
-        <v>6681765</v>
+        <v>6681763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1330,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560757</v>
+        <v>121560740</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
+        <v>90685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,39 +1346,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567080</v>
+        <v>567030</v>
       </c>
       <c r="R8" t="n">
-        <v>6681863</v>
+        <v>6681856</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560761</v>
+        <v>121560745</v>
       </c>
       <c r="B9" t="n">
-        <v>105766</v>
+        <v>91160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567046</v>
+        <v>567091</v>
       </c>
       <c r="R9" t="n">
-        <v>6681865</v>
+        <v>6681781</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,11 +1508,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560746</v>
+        <v>121560761</v>
       </c>
       <c r="B10" t="n">
-        <v>91160</v>
+        <v>105766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,25 +1546,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567115</v>
+        <v>567046</v>
       </c>
       <c r="R10" t="n">
-        <v>6681763</v>
+        <v>6681865</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,6 +1610,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560750</v>
+        <v>121560743</v>
       </c>
       <c r="B11" t="n">
-        <v>91113</v>
+        <v>90720</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,16 +1657,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567116</v>
+        <v>567117</v>
       </c>
       <c r="R11" t="n">
-        <v>6681765</v>
+        <v>6681766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560745</v>
+        <v>121560742</v>
       </c>
       <c r="B12" t="n">
-        <v>91160</v>
+        <v>90720</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,25 +1755,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1783,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567091</v>
+        <v>567120</v>
       </c>
       <c r="R12" t="n">
-        <v>6681781</v>
+        <v>6681651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1845,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560743</v>
+        <v>121560757</v>
       </c>
       <c r="B13" t="n">
-        <v>90720</v>
+        <v>5172</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,38 +1857,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567117</v>
+        <v>567080</v>
       </c>
       <c r="R13" t="n">
-        <v>6681766</v>
+        <v>6681863</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560747</v>
+        <v>121560755</v>
       </c>
       <c r="B14" t="n">
-        <v>91006</v>
+        <v>90933</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1618</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567124</v>
+        <v>567118</v>
       </c>
       <c r="R14" t="n">
-        <v>6681658</v>
+        <v>6681765</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560750</v>
+        <v>121560747</v>
       </c>
       <c r="B5" t="n">
-        <v>91113</v>
+        <v>91006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,16 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567116</v>
+        <v>567124</v>
       </c>
       <c r="R5" t="n">
-        <v>6681765</v>
+        <v>6681658</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560747</v>
+        <v>121560746</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>91160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567124</v>
+        <v>567115</v>
       </c>
       <c r="R6" t="n">
-        <v>6681658</v>
+        <v>6681763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560746</v>
+        <v>121560740</v>
       </c>
       <c r="B7" t="n">
-        <v>91160</v>
+        <v>90685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1240,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1268,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567115</v>
+        <v>567030</v>
       </c>
       <c r="R7" t="n">
-        <v>6681763</v>
+        <v>6681856</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560740</v>
+        <v>121560750</v>
       </c>
       <c r="B8" t="n">
-        <v>90685</v>
+        <v>91113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,25 +1347,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567030</v>
+        <v>567116</v>
       </c>
       <c r="R8" t="n">
-        <v>6681856</v>
+        <v>6681765</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560744</v>
+        <v>121560761</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>105774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,43 +832,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567019</v>
+        <v>567046</v>
       </c>
       <c r="R3" t="n">
-        <v>6681902</v>
+        <v>6681865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,6 +896,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560741</v>
+        <v>121560743</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567125</v>
+        <v>567117</v>
       </c>
       <c r="R4" t="n">
-        <v>6681657</v>
+        <v>6681766</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560747</v>
+        <v>121560742</v>
       </c>
       <c r="B5" t="n">
-        <v>91006</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567124</v>
+        <v>567120</v>
       </c>
       <c r="R5" t="n">
-        <v>6681658</v>
+        <v>6681651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560746</v>
+        <v>121560757</v>
       </c>
       <c r="B6" t="n">
-        <v>91160</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,38 +1143,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567115</v>
+        <v>567080</v>
       </c>
       <c r="R6" t="n">
-        <v>6681763</v>
+        <v>6681863</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1241,7 @@
         <v>121560740</v>
       </c>
       <c r="B7" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,7 +1343,7 @@
         <v>121560750</v>
       </c>
       <c r="B8" t="n">
-        <v>91113</v>
+        <v>91121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560745</v>
+        <v>121560755</v>
       </c>
       <c r="B9" t="n">
-        <v>91160</v>
+        <v>90941</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1618</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567091</v>
+        <v>567118</v>
       </c>
       <c r="R9" t="n">
-        <v>6681781</v>
+        <v>6681765</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560761</v>
+        <v>121560747</v>
       </c>
       <c r="B10" t="n">
-        <v>105766</v>
+        <v>91014</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,25 +1551,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567046</v>
+        <v>567124</v>
       </c>
       <c r="R10" t="n">
-        <v>6681865</v>
+        <v>6681658</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,11 +1615,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1641,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560743</v>
+        <v>121560744</v>
       </c>
       <c r="B11" t="n">
-        <v>90720</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,34 +1657,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567117</v>
+        <v>567019</v>
       </c>
       <c r="R11" t="n">
-        <v>6681766</v>
+        <v>6681902</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560742</v>
+        <v>121560745</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
+        <v>91168</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1783,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567120</v>
+        <v>567091</v>
       </c>
       <c r="R12" t="n">
-        <v>6681651</v>
+        <v>6681781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560757</v>
+        <v>121560741</v>
       </c>
       <c r="B13" t="n">
-        <v>5172</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,43 +1862,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567080</v>
+        <v>567125</v>
       </c>
       <c r="R13" t="n">
-        <v>6681863</v>
+        <v>6681657</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560755</v>
+        <v>121560746</v>
       </c>
       <c r="B14" t="n">
-        <v>90933</v>
+        <v>91168</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1968,21 +1968,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1618</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567118</v>
+        <v>567115</v>
       </c>
       <c r="R14" t="n">
-        <v>6681765</v>
+        <v>6681763</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560747</v>
+        <v>121560741</v>
       </c>
       <c r="B3" t="n">
-        <v>91014</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,21 +836,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567124</v>
+        <v>567125</v>
       </c>
       <c r="R3" t="n">
-        <v>6681658</v>
+        <v>6681657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560746</v>
+        <v>121560747</v>
       </c>
       <c r="B4" t="n">
-        <v>91168</v>
+        <v>91014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567115</v>
+        <v>567124</v>
       </c>
       <c r="R4" t="n">
-        <v>6681763</v>
+        <v>6681658</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560750</v>
+        <v>121560743</v>
       </c>
       <c r="B5" t="n">
-        <v>91121</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,16 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567116</v>
+        <v>567117</v>
       </c>
       <c r="R5" t="n">
-        <v>6681765</v>
+        <v>6681766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560744</v>
+        <v>121560761</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>105774</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,43 +1138,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567019</v>
+        <v>567046</v>
       </c>
       <c r="R6" t="n">
-        <v>6681902</v>
+        <v>6681865</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,6 +1202,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560761</v>
+        <v>121560757</v>
       </c>
       <c r="B8" t="n">
-        <v>105774</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,38 +1347,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567046</v>
+        <v>567080</v>
       </c>
       <c r="R8" t="n">
-        <v>6681865</v>
+        <v>6681863</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,11 +1416,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560757</v>
+        <v>121560744</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,31 +1454,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1482,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567080</v>
+        <v>567019</v>
       </c>
       <c r="R9" t="n">
-        <v>6681863</v>
+        <v>6681902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1748,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560741</v>
+        <v>121560746</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>91168</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,25 +1765,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567125</v>
+        <v>567115</v>
       </c>
       <c r="R12" t="n">
-        <v>6681657</v>
+        <v>6681763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560743</v>
+        <v>121560740</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1867,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567117</v>
+        <v>567030</v>
       </c>
       <c r="R13" t="n">
-        <v>6681766</v>
+        <v>6681856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560740</v>
+        <v>121560750</v>
       </c>
       <c r="B14" t="n">
-        <v>90693</v>
+        <v>91121</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1969,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567030</v>
+        <v>567116</v>
       </c>
       <c r="R14" t="n">
-        <v>6681856</v>
+        <v>6681765</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560746</v>
+        <v>121560740</v>
       </c>
       <c r="B12" t="n">
-        <v>91168</v>
+        <v>90693</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,25 +1765,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567115</v>
+        <v>567030</v>
       </c>
       <c r="R12" t="n">
-        <v>6681763</v>
+        <v>6681856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560740</v>
+        <v>121560746</v>
       </c>
       <c r="B13" t="n">
-        <v>90693</v>
+        <v>91168</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,25 +1867,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567030</v>
+        <v>567115</v>
       </c>
       <c r="R13" t="n">
-        <v>6681856</v>
+        <v>6681763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560741</v>
+        <v>121560755</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>90941</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567125</v>
+        <v>567118</v>
       </c>
       <c r="R3" t="n">
-        <v>6681657</v>
+        <v>6681765</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560747</v>
+        <v>121560740</v>
       </c>
       <c r="B4" t="n">
-        <v>91014</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567124</v>
+        <v>567030</v>
       </c>
       <c r="R4" t="n">
-        <v>6681658</v>
+        <v>6681856</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560743</v>
+        <v>121560742</v>
       </c>
       <c r="B5" t="n">
         <v>90728</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567117</v>
+        <v>567120</v>
       </c>
       <c r="R5" t="n">
-        <v>6681766</v>
+        <v>6681651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560761</v>
+        <v>121560747</v>
       </c>
       <c r="B6" t="n">
-        <v>105774</v>
+        <v>91014</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,25 +1138,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220785</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567046</v>
+        <v>567124</v>
       </c>
       <c r="R6" t="n">
-        <v>6681865</v>
+        <v>6681658</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,11 +1202,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560745</v>
+        <v>121560744</v>
       </c>
       <c r="B7" t="n">
-        <v>91168</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,38 +1240,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567091</v>
+        <v>567019</v>
       </c>
       <c r="R7" t="n">
-        <v>6681781</v>
+        <v>6681902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560744</v>
+        <v>121560745</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>91168</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,43 +1454,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567019</v>
+        <v>567091</v>
       </c>
       <c r="R9" t="n">
-        <v>6681902</v>
+        <v>6681781</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560755</v>
+        <v>121560746</v>
       </c>
       <c r="B10" t="n">
-        <v>90941</v>
+        <v>91168</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1618</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567118</v>
+        <v>567115</v>
       </c>
       <c r="R10" t="n">
-        <v>6681765</v>
+        <v>6681763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1646,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560742</v>
+        <v>121560741</v>
       </c>
       <c r="B11" t="n">
         <v>90728</v>
@@ -1691,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567120</v>
+        <v>567125</v>
       </c>
       <c r="R11" t="n">
-        <v>6681651</v>
+        <v>6681657</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560740</v>
+        <v>121560743</v>
       </c>
       <c r="B12" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1765,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1793,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567030</v>
+        <v>567117</v>
       </c>
       <c r="R12" t="n">
-        <v>6681856</v>
+        <v>6681766</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560746</v>
+        <v>121560761</v>
       </c>
       <c r="B13" t="n">
-        <v>91168</v>
+        <v>105774</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1867,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567115</v>
+        <v>567046</v>
       </c>
       <c r="R13" t="n">
-        <v>6681763</v>
+        <v>6681865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,6 +1926,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560757</v>
+        <v>121560745</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>91168</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,43 +1347,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567080</v>
+        <v>567091</v>
       </c>
       <c r="R8" t="n">
-        <v>6681863</v>
+        <v>6681781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1437,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560745</v>
+        <v>121560746</v>
       </c>
       <c r="B9" t="n">
         <v>91168</v>
@@ -1482,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567091</v>
+        <v>567115</v>
       </c>
       <c r="R9" t="n">
-        <v>6681781</v>
+        <v>6681763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560746</v>
+        <v>121560757</v>
       </c>
       <c r="B10" t="n">
-        <v>91168</v>
+        <v>5173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,38 +1551,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567115</v>
+        <v>567080</v>
       </c>
       <c r="R10" t="n">
-        <v>6681763</v>
+        <v>6681863</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560755</v>
+        <v>121560746</v>
       </c>
       <c r="B3" t="n">
-        <v>90941</v>
+        <v>91168</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,21 +836,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1618</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567118</v>
+        <v>567115</v>
       </c>
       <c r="R3" t="n">
-        <v>6681765</v>
+        <v>6681763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560740</v>
+        <v>121560741</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567030</v>
+        <v>567125</v>
       </c>
       <c r="R4" t="n">
-        <v>6681856</v>
+        <v>6681657</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560742</v>
+        <v>121560747</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>91014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567120</v>
+        <v>567124</v>
       </c>
       <c r="R5" t="n">
-        <v>6681651</v>
+        <v>6681658</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560747</v>
+        <v>121560757</v>
       </c>
       <c r="B6" t="n">
-        <v>91014</v>
+        <v>5173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,38 +1138,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567124</v>
+        <v>567080</v>
       </c>
       <c r="R6" t="n">
-        <v>6681658</v>
+        <v>6681863</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560744</v>
+        <v>121560742</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,39 +1249,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567019</v>
+        <v>567120</v>
       </c>
       <c r="R7" t="n">
-        <v>6681902</v>
+        <v>6681651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560745</v>
+        <v>121560761</v>
       </c>
       <c r="B8" t="n">
-        <v>91168</v>
+        <v>105774</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220785</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567091</v>
+        <v>567046</v>
       </c>
       <c r="R8" t="n">
-        <v>6681781</v>
+        <v>6681865</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560746</v>
+        <v>121560744</v>
       </c>
       <c r="B9" t="n">
-        <v>91168</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,38 +1454,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567115</v>
+        <v>567019</v>
       </c>
       <c r="R9" t="n">
-        <v>6681763</v>
+        <v>6681902</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560757</v>
+        <v>121560743</v>
       </c>
       <c r="B10" t="n">
-        <v>5173</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,43 +1561,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567080</v>
+        <v>567117</v>
       </c>
       <c r="R10" t="n">
-        <v>6681863</v>
+        <v>6681766</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1646,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560741</v>
+        <v>121560750</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>91121</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,21 +1667,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567125</v>
+        <v>567116</v>
       </c>
       <c r="R11" t="n">
-        <v>6681657</v>
+        <v>6681765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560743</v>
+        <v>121560740</v>
       </c>
       <c r="B12" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567117</v>
+        <v>567030</v>
       </c>
       <c r="R12" t="n">
-        <v>6681766</v>
+        <v>6681856</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560761</v>
+        <v>121560745</v>
       </c>
       <c r="B13" t="n">
-        <v>105774</v>
+        <v>91168</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567046</v>
+        <v>567091</v>
       </c>
       <c r="R13" t="n">
-        <v>6681865</v>
+        <v>6681781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,11 +1926,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560750</v>
+        <v>121560755</v>
       </c>
       <c r="B14" t="n">
-        <v>91121</v>
+        <v>90941</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1969,20 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>1618</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567116</v>
+        <v>567118</v>
       </c>
       <c r="R14" t="n">
         <v>6681765</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560746</v>
+        <v>121560741</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567115</v>
+        <v>567125</v>
       </c>
       <c r="R3" t="n">
-        <v>6681763</v>
+        <v>6681657</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560741</v>
+        <v>121560744</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,34 +938,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567125</v>
+        <v>567019</v>
       </c>
       <c r="R4" t="n">
-        <v>6681657</v>
+        <v>6681902</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560747</v>
+        <v>121560746</v>
       </c>
       <c r="B5" t="n">
-        <v>91014</v>
+        <v>91168</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,25 +1041,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567124</v>
+        <v>567115</v>
       </c>
       <c r="R5" t="n">
-        <v>6681658</v>
+        <v>6681763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560757</v>
+        <v>121560745</v>
       </c>
       <c r="B6" t="n">
-        <v>5173</v>
+        <v>91168</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,43 +1143,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567080</v>
+        <v>567091</v>
       </c>
       <c r="R6" t="n">
-        <v>6681863</v>
+        <v>6681781</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560742</v>
+        <v>121560757</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>5173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,38 +1245,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567120</v>
+        <v>567080</v>
       </c>
       <c r="R7" t="n">
-        <v>6681651</v>
+        <v>6681863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560761</v>
+        <v>121560743</v>
       </c>
       <c r="B8" t="n">
-        <v>105774</v>
+        <v>90728</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,25 +1352,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567046</v>
+        <v>567117</v>
       </c>
       <c r="R8" t="n">
-        <v>6681865</v>
+        <v>6681766</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,11 +1416,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560744</v>
+        <v>121560742</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,39 +1458,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567019</v>
+        <v>567120</v>
       </c>
       <c r="R9" t="n">
-        <v>6681902</v>
+        <v>6681651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560743</v>
+        <v>121560761</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>105774</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1561,25 +1556,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220785</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567117</v>
+        <v>567046</v>
       </c>
       <c r="R10" t="n">
-        <v>6681766</v>
+        <v>6681865</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,6 +1620,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560740</v>
+        <v>121560755</v>
       </c>
       <c r="B12" t="n">
-        <v>90693</v>
+        <v>90941</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1618</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567030</v>
+        <v>567118</v>
       </c>
       <c r="R12" t="n">
-        <v>6681856</v>
+        <v>6681765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560745</v>
+        <v>121560740</v>
       </c>
       <c r="B13" t="n">
-        <v>91168</v>
+        <v>90693</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567091</v>
+        <v>567030</v>
       </c>
       <c r="R13" t="n">
-        <v>6681781</v>
+        <v>6681856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560755</v>
+        <v>121560747</v>
       </c>
       <c r="B14" t="n">
-        <v>90941</v>
+        <v>91014</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1618</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567118</v>
+        <v>567124</v>
       </c>
       <c r="R14" t="n">
-        <v>6681765</v>
+        <v>6681658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560741</v>
+        <v>121560740</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>90693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567125</v>
+        <v>567030</v>
       </c>
       <c r="R3" t="n">
-        <v>6681657</v>
+        <v>6681856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560744</v>
+        <v>121560750</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>91121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,39 +938,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567019</v>
+        <v>567116</v>
       </c>
       <c r="R4" t="n">
-        <v>6681902</v>
+        <v>6681765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560746</v>
+        <v>121560743</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,25 +1031,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567115</v>
+        <v>567117</v>
       </c>
       <c r="R5" t="n">
-        <v>6681763</v>
+        <v>6681766</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560745</v>
+        <v>121560742</v>
       </c>
       <c r="B6" t="n">
-        <v>91168</v>
+        <v>90728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567091</v>
+        <v>567120</v>
       </c>
       <c r="R6" t="n">
-        <v>6681781</v>
+        <v>6681651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560757</v>
+        <v>121560746</v>
       </c>
       <c r="B7" t="n">
-        <v>5173</v>
+        <v>91168</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,43 +1235,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567080</v>
+        <v>567115</v>
       </c>
       <c r="R7" t="n">
-        <v>6681863</v>
+        <v>6681763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1325,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560743</v>
+        <v>121560741</v>
       </c>
       <c r="B8" t="n">
         <v>90728</v>
@@ -1380,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567117</v>
+        <v>567125</v>
       </c>
       <c r="R8" t="n">
-        <v>6681766</v>
+        <v>6681657</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560742</v>
+        <v>121560757</v>
       </c>
       <c r="B9" t="n">
-        <v>90728</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,38 +1439,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567120</v>
+        <v>567080</v>
       </c>
       <c r="R9" t="n">
-        <v>6681651</v>
+        <v>6681863</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1544,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560761</v>
+        <v>121560755</v>
       </c>
       <c r="B10" t="n">
-        <v>105774</v>
+        <v>90941</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,25 +1546,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>1618</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1584,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567046</v>
+        <v>567118</v>
       </c>
       <c r="R10" t="n">
-        <v>6681865</v>
+        <v>6681765</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,11 +1610,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560750</v>
+        <v>121560761</v>
       </c>
       <c r="B11" t="n">
-        <v>91121</v>
+        <v>105774</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,20 +1648,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1686,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567116</v>
+        <v>567046</v>
       </c>
       <c r="R11" t="n">
-        <v>6681765</v>
+        <v>6681865</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,6 +1712,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560755</v>
+        <v>121560744</v>
       </c>
       <c r="B12" t="n">
-        <v>90941</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,38 +1755,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1618</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567118</v>
+        <v>567019</v>
       </c>
       <c r="R12" t="n">
-        <v>6681765</v>
+        <v>6681902</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560740</v>
+        <v>121560747</v>
       </c>
       <c r="B13" t="n">
-        <v>90693</v>
+        <v>91014</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567030</v>
+        <v>567124</v>
       </c>
       <c r="R13" t="n">
-        <v>6681856</v>
+        <v>6681658</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560747</v>
+        <v>121560745</v>
       </c>
       <c r="B14" t="n">
-        <v>91014</v>
+        <v>91168</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1964,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567124</v>
+        <v>567091</v>
       </c>
       <c r="R14" t="n">
-        <v>6681658</v>
+        <v>6681781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -820,10 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560740</v>
+        <v>121560742</v>
       </c>
       <c r="B3" t="n">
-        <v>90693</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,25 +832,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567030</v>
+        <v>567120</v>
       </c>
       <c r="R3" t="n">
-        <v>6681856</v>
+        <v>6681651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560750</v>
+        <v>121560745</v>
       </c>
       <c r="B4" t="n">
-        <v>91121</v>
+        <v>91168</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,20 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>1209</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +962,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567116</v>
+        <v>567091</v>
       </c>
       <c r="R4" t="n">
-        <v>6681765</v>
+        <v>6681781</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560743</v>
+        <v>121560746</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>91168</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,25 +1036,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567117</v>
+        <v>567115</v>
       </c>
       <c r="R5" t="n">
-        <v>6681766</v>
+        <v>6681763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560742</v>
+        <v>121560747</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>91014</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1142,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567120</v>
+        <v>567124</v>
       </c>
       <c r="R6" t="n">
-        <v>6681651</v>
+        <v>6681658</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560746</v>
+        <v>121560750</v>
       </c>
       <c r="B7" t="n">
-        <v>91168</v>
+        <v>91121</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,25 +1240,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567115</v>
+        <v>567116</v>
       </c>
       <c r="R7" t="n">
-        <v>6681763</v>
+        <v>6681765</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1534,10 +1534,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560755</v>
+        <v>121560740</v>
       </c>
       <c r="B10" t="n">
-        <v>90941</v>
+        <v>90693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1618</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567118</v>
+        <v>567030</v>
       </c>
       <c r="R10" t="n">
-        <v>6681765</v>
+        <v>6681856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,10 +1636,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560761</v>
+        <v>121560743</v>
       </c>
       <c r="B11" t="n">
-        <v>105774</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,25 +1648,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567046</v>
+        <v>567117</v>
       </c>
       <c r="R11" t="n">
-        <v>6681865</v>
+        <v>6681766</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1712,11 +1712,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1743,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560744</v>
+        <v>121560755</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>90941</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,43 +1750,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1618</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567019</v>
+        <v>567118</v>
       </c>
       <c r="R12" t="n">
-        <v>6681902</v>
+        <v>6681765</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1850,10 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560747</v>
+        <v>121560744</v>
       </c>
       <c r="B13" t="n">
-        <v>91014</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1866,34 +1856,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567124</v>
+        <v>567019</v>
       </c>
       <c r="R13" t="n">
-        <v>6681658</v>
+        <v>6681902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560745</v>
+        <v>121560761</v>
       </c>
       <c r="B14" t="n">
-        <v>91168</v>
+        <v>105774</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,25 +1959,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1992,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567091</v>
+        <v>567046</v>
       </c>
       <c r="R14" t="n">
-        <v>6681781</v>
+        <v>6681865</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,6 +2023,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2052,6 +2052,215 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123412895</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100634</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567101</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6681830</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123412893</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91716</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>366</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567160</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6681722</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123412895</v>
+        <v>123412893</v>
       </c>
       <c r="B15" t="n">
-        <v>100634</v>
+        <v>91716</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2066,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567101</v>
+        <v>567160</v>
       </c>
       <c r="R15" t="n">
-        <v>6681830</v>
+        <v>6681722</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,6 +2130,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123412893</v>
+        <v>123412895</v>
       </c>
       <c r="B16" t="n">
-        <v>91716</v>
+        <v>100634</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,25 +2173,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567160</v>
+        <v>567101</v>
       </c>
       <c r="R16" t="n">
-        <v>6681722</v>
+        <v>6681830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,11 +2237,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2057,7 +2057,7 @@
         <v>123412893</v>
       </c>
       <c r="B15" t="n">
-        <v>91716</v>
+        <v>91718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>123412895</v>
       </c>
       <c r="B16" t="n">
-        <v>100634</v>
+        <v>100636</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123412893</v>
+        <v>123412895</v>
       </c>
       <c r="B15" t="n">
-        <v>91718</v>
+        <v>100642</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2066,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567160</v>
+        <v>567101</v>
       </c>
       <c r="R15" t="n">
-        <v>6681722</v>
+        <v>6681830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,11 +2130,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123412895</v>
+        <v>123412893</v>
       </c>
       <c r="B16" t="n">
-        <v>100636</v>
+        <v>91724</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,25 +2168,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567101</v>
+        <v>567160</v>
       </c>
       <c r="R16" t="n">
-        <v>6681830</v>
+        <v>6681722</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,6 +2232,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2057,7 +2057,7 @@
         <v>123412895</v>
       </c>
       <c r="B15" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>123412893</v>
       </c>
       <c r="B16" t="n">
-        <v>91727</v>
+        <v>91744</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2057,7 +2057,7 @@
         <v>123412895</v>
       </c>
       <c r="B15" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>123412893</v>
       </c>
       <c r="B16" t="n">
-        <v>91744</v>
+        <v>91749</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2057,7 +2057,7 @@
         <v>123412895</v>
       </c>
       <c r="B15" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>123412893</v>
       </c>
       <c r="B16" t="n">
-        <v>91749</v>
+        <v>91751</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123412895</v>
+        <v>123412893</v>
       </c>
       <c r="B15" t="n">
-        <v>100682</v>
+        <v>91751</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2066,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567101</v>
+        <v>567160</v>
       </c>
       <c r="R15" t="n">
-        <v>6681830</v>
+        <v>6681722</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,6 +2130,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123412893</v>
+        <v>123412895</v>
       </c>
       <c r="B16" t="n">
-        <v>91751</v>
+        <v>100257</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,25 +2173,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567160</v>
+        <v>567101</v>
       </c>
       <c r="R16" t="n">
-        <v>6681722</v>
+        <v>6681830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,11 +2237,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123412893</v>
+        <v>123412895</v>
       </c>
       <c r="B15" t="n">
-        <v>91751</v>
+        <v>100257</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2066,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567160</v>
+        <v>567101</v>
       </c>
       <c r="R15" t="n">
-        <v>6681722</v>
+        <v>6681830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,11 +2130,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2156,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123412895</v>
+        <v>123412893</v>
       </c>
       <c r="B16" t="n">
-        <v>100257</v>
+        <v>91751</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2173,25 +2168,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2196,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567101</v>
+        <v>567160</v>
       </c>
       <c r="R16" t="n">
-        <v>6681830</v>
+        <v>6681722</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,6 +2232,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2054,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123412895</v>
+        <v>123412893</v>
       </c>
       <c r="B15" t="n">
-        <v>100257</v>
+        <v>91751</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2066,25 +2066,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567101</v>
+        <v>567160</v>
       </c>
       <c r="R15" t="n">
-        <v>6681830</v>
+        <v>6681722</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,6 +2130,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123412893</v>
+        <v>123412895</v>
       </c>
       <c r="B16" t="n">
-        <v>91751</v>
+        <v>100257</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2168,25 +2173,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2196,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567160</v>
+        <v>567101</v>
       </c>
       <c r="R16" t="n">
-        <v>6681722</v>
+        <v>6681830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2232,11 +2237,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2261,6 +2261,117 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124825322</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103528</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Garpenberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567117</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6681655</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>124825322</v>
       </c>
       <c r="B17" t="n">
-        <v>103528</v>
+        <v>103700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2268,11 +2268,6 @@
       <c r="B17" t="n">
         <v>103700</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>LC</t>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2367,6 +2367,642 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128064389</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92276</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567009</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6681903</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128064398</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92630</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum fennicum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567100</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6681592</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128064388</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92276</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567054</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6681878</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128064387</v>
+      </c>
+      <c r="B21" t="n">
+        <v>103904</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567108</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6681676</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128064399</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92630</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum fennicum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567103</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6681598</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128064390</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92276</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567036</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6681890</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2475,37 +2475,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128064398</v>
+        <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92630</v>
+        <v>92276</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1435</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567100</v>
+        <v>567054</v>
       </c>
       <c r="R19" t="n">
-        <v>6681592</v>
+        <v>6681878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2581,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128064388</v>
+        <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>92276</v>
+        <v>103904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,31 +2592,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2625,10 +2625,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567054</v>
+        <v>567108</v>
       </c>
       <c r="R20" t="n">
-        <v>6681878</v>
+        <v>6681676</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2687,42 +2687,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128064387</v>
+        <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>103904</v>
+        <v>92630</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222412</v>
+        <v>1435</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567108</v>
+        <v>567103</v>
       </c>
       <c r="R21" t="n">
-        <v>6681676</v>
+        <v>6681598</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,37 +2793,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128064399</v>
+        <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92630</v>
+        <v>92276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1435</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2837,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567103</v>
+        <v>567036</v>
       </c>
       <c r="R22" t="n">
-        <v>6681598</v>
+        <v>6681890</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,37 +2899,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128064390</v>
+        <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92276</v>
+        <v>92630</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4769</v>
+        <v>1435</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567036</v>
+        <v>567100</v>
       </c>
       <c r="R23" t="n">
-        <v>6681890</v>
+        <v>6681592</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>128064389</v>
       </c>
       <c r="B18" t="n">
-        <v>92276</v>
+        <v>92284</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92276</v>
+        <v>92284</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>103904</v>
+        <v>103912</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>92630</v>
+        <v>92638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92276</v>
+        <v>92284</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92630</v>
+        <v>92638</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>128064389</v>
       </c>
       <c r="B18" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>103912</v>
+        <v>103913</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>92638</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92638</v>
+        <v>92639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>128064389</v>
       </c>
       <c r="B18" t="n">
-        <v>92285</v>
+        <v>92286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92285</v>
+        <v>92286</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>103913</v>
+        <v>103914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92285</v>
+        <v>92286</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>128064389</v>
       </c>
       <c r="B18" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>103914</v>
+        <v>103915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>128064389</v>
       </c>
       <c r="B18" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>103915</v>
+        <v>103923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>92641</v>
+        <v>92649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92287</v>
+        <v>92295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92641</v>
+        <v>92649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>128064389</v>
       </c>
       <c r="B18" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>103923</v>
+        <v>104016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>92649</v>
+        <v>92741</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92649</v>
+        <v>92741</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2372,7 +2372,7 @@
         <v>128064389</v>
       </c>
       <c r="B18" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>128064388</v>
       </c>
       <c r="B19" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>128064387</v>
       </c>
       <c r="B20" t="n">
-        <v>104016</v>
+        <v>104036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>128064399</v>
       </c>
       <c r="B21" t="n">
-        <v>92741</v>
+        <v>92753</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>128064390</v>
       </c>
       <c r="B22" t="n">
-        <v>92387</v>
+        <v>92399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92741</v>
+        <v>92753</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -2902,7 +2902,7 @@
         <v>128064398</v>
       </c>
       <c r="B23" t="n">
-        <v>92753</v>
+        <v>92755</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61279027</v>
+        <v>123412893</v>
       </c>
       <c r="B2" t="n">
-        <v>89742</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1506</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567076.8527146991</v>
+        <v>567160</v>
       </c>
       <c r="R2" t="n">
-        <v>6681777.207209136</v>
+        <v>6681722</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,88 +740,47 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>med inslag av asp</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # mycket grov granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121560742</v>
+        <v>121560747</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -860,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567120</v>
+        <v>567124</v>
       </c>
       <c r="R3" t="n">
-        <v>6681651</v>
+        <v>6681658</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -922,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121560745</v>
+        <v>121560748</v>
       </c>
       <c r="B4" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567091</v>
+        <v>567118</v>
       </c>
       <c r="R4" t="n">
-        <v>6681781</v>
+        <v>6681768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121560746</v>
+        <v>121560741</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567115</v>
+        <v>567125</v>
       </c>
       <c r="R5" t="n">
-        <v>6681763</v>
+        <v>6681657</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,15 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121560747</v>
+        <v>121560742</v>
       </c>
       <c r="B6" t="n">
-        <v>91014</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567124</v>
+        <v>567120</v>
       </c>
       <c r="R6" t="n">
-        <v>6681658</v>
+        <v>6681651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121560750</v>
+        <v>121560743</v>
       </c>
       <c r="B7" t="n">
-        <v>91121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,16 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567116</v>
+        <v>567117</v>
       </c>
       <c r="R7" t="n">
-        <v>6681765</v>
+        <v>6681766</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,15 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121560741</v>
+        <v>121560745</v>
       </c>
       <c r="B8" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567125</v>
+        <v>567091</v>
       </c>
       <c r="R8" t="n">
-        <v>6681657</v>
+        <v>6681781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,55 +1359,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121560757</v>
+        <v>121560746</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567080</v>
+        <v>567115</v>
       </c>
       <c r="R9" t="n">
-        <v>6681863</v>
+        <v>6681763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1534,50 +1456,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121560740</v>
+        <v>128064398</v>
       </c>
       <c r="B10" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1435</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567030</v>
+        <v>567100</v>
       </c>
       <c r="R10" t="n">
-        <v>6681856</v>
+        <v>6681592</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,12 +1530,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1636,50 +1562,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121560743</v>
+        <v>128064399</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1435</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567117</v>
+        <v>567103</v>
       </c>
       <c r="R11" t="n">
-        <v>6681766</v>
+        <v>6681598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,12 +1636,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1738,15 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121560755</v>
+        <v>61279027</v>
       </c>
       <c r="B12" t="n">
-        <v>90941</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,37 +1679,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1618</v>
+        <v>1506</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567118</v>
+        <v>567077</v>
       </c>
       <c r="R12" t="n">
-        <v>6681765</v>
+        <v>6681777</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,47 +1735,73 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2016-09-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2016-09-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>med inslag av asp</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # mycket grov granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121560744</v>
+        <v>121560755</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1856,39 +1809,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>1618</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567019</v>
+        <v>567118</v>
       </c>
       <c r="R13" t="n">
-        <v>6681902</v>
+        <v>6681765</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,50 +1895,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121560761</v>
+        <v>128064388</v>
       </c>
       <c r="B14" t="n">
-        <v>105774</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567046</v>
+        <v>567054</v>
       </c>
       <c r="R14" t="n">
-        <v>6681865</v>
+        <v>6681878</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,17 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ungträd</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2054,50 +2001,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123412893</v>
+        <v>128064389</v>
       </c>
       <c r="B15" t="n">
-        <v>91773</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567160</v>
+        <v>567009</v>
       </c>
       <c r="R15" t="n">
-        <v>6681722</v>
+        <v>6681903</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,17 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gamla fruktkroppar</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,15 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123412895</v>
+        <v>128064390</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2177,34 +2118,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567101</v>
+        <v>567036</v>
       </c>
       <c r="R16" t="n">
-        <v>6681830</v>
+        <v>6681890</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,12 +2181,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2213,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124825322</v>
+        <v>121560740</v>
       </c>
       <c r="B17" t="n">
-        <v>103700</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,38 +2224,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Garpenberg, Dlr</t>
+          <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567117</v>
+        <v>567030</v>
       </c>
       <c r="R17" t="n">
-        <v>6681655</v>
+        <v>6681856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,17 +2278,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,22 +2298,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128064389</v>
+        <v>121560744</v>
       </c>
       <c r="B18" t="n">
-        <v>92399</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,31 +2321,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2413,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567009</v>
+        <v>567019</v>
       </c>
       <c r="R18" t="n">
-        <v>6681903</v>
+        <v>6681902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,12 +2380,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2475,10 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128064388</v>
+        <v>121560757</v>
       </c>
       <c r="B19" t="n">
-        <v>92399</v>
+        <v>5179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2486,31 +2423,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2519,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567054</v>
+        <v>567080</v>
       </c>
       <c r="R19" t="n">
-        <v>6681878</v>
+        <v>6681863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,12 +2482,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,27 +2514,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128064387</v>
+        <v>121560761</v>
       </c>
       <c r="B20" t="n">
-        <v>104036</v>
+        <v>106813</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2609,26 +2542,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brattfors, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567108</v>
+        <v>567046</v>
       </c>
       <c r="R20" t="n">
-        <v>6681676</v>
+        <v>6681865</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,12 +2579,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ungträd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2687,10 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128064399</v>
+        <v>117766275</v>
       </c>
       <c r="B21" t="n">
-        <v>92753</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,46 +2627,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1435</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Brattfors, Dlr</t>
+          <t>Garpenberg, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567103</v>
+        <v>567135</v>
       </c>
       <c r="R21" t="n">
-        <v>6681598</v>
+        <v>6681730</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2761,12 +2685,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2781,22 +2710,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128064390</v>
+        <v>124825322</v>
       </c>
       <c r="B22" t="n">
-        <v>92399</v>
+        <v>104628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2804,21 +2733,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2826,21 +2755,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brattfors, Dlr</t>
+          <t>Garpenberg, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567036</v>
+        <v>567117</v>
       </c>
       <c r="R22" t="n">
-        <v>6681890</v>
+        <v>6681655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,12 +2791,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,54 +2816,54 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128064398</v>
+        <v>128064387</v>
       </c>
       <c r="B23" t="n">
-        <v>92755</v>
+        <v>104628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1435</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2943,10 +2872,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567100</v>
+        <v>567108</v>
       </c>
       <c r="R23" t="n">
-        <v>6681592</v>
+        <v>6681676</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3002,6 +2931,200 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123412895</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567101</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6681830</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121560750</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brattfors, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>567116</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6681765</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56932-2024 artfynd.xlsx
+++ b/artfynd/A 56932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560747</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560748</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560741</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560742</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560743</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560745</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560746</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064398</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064399</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61279027</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,6 +1952,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560755</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064388</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064389</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,6 +2285,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064390</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560740</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560744</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560757</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560761</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766275</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2825,6 +2930,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124825322</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2931,6 +3041,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128064387</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3028,6 +3143,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412895</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3125,8 +3245,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121560750</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>